--- a/author.xlsx
+++ b/author.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0294DCD-E2BA-4AE4-8DB0-AF5752D93520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADAC4891-4566-44CB-AB2C-B28DADD93250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project" sheetId="4" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="55">
   <si>
     <t>Short Description</t>
   </si>
@@ -171,9 +171,6 @@
 A Random Forest regression model predicts a baseline alpha value based on these study features. The predicted value is then adjusted using contextual factors such as risk tolerance, test direction, and the number of hypothesis tests. This approach allows the system to provide more flexible and context-aware statistical decision support.</t>
   </si>
   <si>
-    <t>&lt;30&gt;</t>
-  </si>
-  <si>
     <t>&lt;Prof. Dr. Joachim Schwarz&gt;</t>
   </si>
   <si>
@@ -184,6 +181,12 @@
   </si>
   <si>
     <t>joachim.schwarz(at)hs-emden-leer.de</t>
+  </si>
+  <si>
+    <t>Master Thesis</t>
+  </si>
+  <si>
+    <t>&lt;28&gt;</t>
   </si>
 </sst>
 </file>
@@ -697,13 +700,16 @@
       <c r="A15" s="3" t="s">
         <v>30</v>
       </c>
+      <c r="B15" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -805,20 +811,23 @@
         <v>29</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="B39" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
@@ -840,7 +849,7 @@
         <v>29</v>
       </c>
       <c r="B45" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
@@ -856,7 +865,7 @@
         <v>13</v>
       </c>
       <c r="B47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
